--- a/backend/internal/partsimport/parts_import_template.xlsx
+++ b/backend/internal/partsimport/parts_import_template.xlsx
@@ -257,39 +257,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">สายไฟ VAF 2*1.5 (100ม)</t>
+          <t xml:space="preserve">ขั้วยางกันน้ำ</t>
         </is>
       </c>
       <c r="B4">
-        <v>1400</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>859</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">P9001</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8851234567890</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">เส้น</t>
-        </is>
-      </c>
+          <t xml:space="preserve">P0140</t>
+        </is>
+      </c>
+      <c r="F4"/>
+      <c r="G4"/>
       <c r="H4"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B-12</t>
-        </is>
-      </c>
+      <c r="I4"/>
       <c r="J4"/>
     </row>
     <row r="5"/>
@@ -310,40 +298,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">• รหัสสินค้า — เว้นว่างไว้ ระบบจะออกให้อัตโนมัติ (P0001, P0002, ...)</t>
+          <t xml:space="preserve">• รหัสสินค้า — เว้นว่างไว้ = สินค้าใหม่ ระบบจะออกรหัสให้อัตโนมัติ (P0001, P0002, ...)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">• บาร์โค้ด — เว้นว่างไว้ ระบบจะใช้รหัสสินค้าเป็นบาร์โค้ด</t>
+          <t xml:space="preserve">• กรอกรหัสสินค้าที่มีอยู่แล้ว = อัปเดตของเดิม จำนวนจะถูกบวกเพิ่มเข้าคลัง และแก้ต้นทุน/ราคาให้</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">• หน่วย — เว้นว่างไว้ ระบบจะใช้ "pcs" (ชิ้น) ถ้ากรอกหน่วยที่ไม่มีในระบบจะถูกเว้นว่าง</t>
+          <t xml:space="preserve">  ส่วนชื่อสินค้าและบาร์โค้ดจะไม่ถูกแก้ ต้องไปกดแก้ไขที่หน้าสินค้าเท่านั้น</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">• ราคาขายขั้นต่ำ — เว้นว่างไว้ ระบบจะคิดให้เป็น 90% ของราคาขาย และต้องไม่เกินราคาขาย</t>
+          <t xml:space="preserve">• บาร์โค้ด — เว้นว่างไว้ ระบบจะใช้รหัสสินค้าเป็นบาร์โค้ด</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">• จำนวนที่รับเข้าคลังหลัก — สินค้าใหม่เข้าคลังหลักเท่านั้น เว้นว่าง = 0</t>
+          <t xml:space="preserve">• หน่วย — เว้นว่างไว้ ระบบจะใช้ "pcs" (ชิ้น) ถ้ากรอกหน่วยที่ไม่มีในระบบจะถูกเว้นว่าง</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• ราคาขายขั้นต่ำ — เว้นว่างไว้ ระบบจะคิดให้เป็น 90% ของราคาขาย และต้องไม่เกินราคาขาย</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• จำนวนที่รับเข้าคลังหลัก — สินค้าใหม่เข้าคลังหลักเท่านั้น เว้นว่าง = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t xml:space="preserve">• ห้ามแก้ไข ลบ หรือสลับหัวคอลัมน์ในแถวที่ 1 ของชีต "สินค้า"</t>
         </is>

--- a/backend/internal/partsimport/parts_import_template.xlsx
+++ b/backend/internal/partsimport/parts_import_template.xlsx
@@ -298,14 +298,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">• รหัสสินค้า — เว้นว่างไว้ = สินค้าใหม่ ระบบจะออกรหัสให้อัตโนมัติ (P0001, P0002, ...)</t>
+          <t xml:space="preserve">• ถ้ารหัสสินค้า หรือ ชื่อสินค้า ตรงกับของที่มีอยู่แล้ว = อัปเดตของเดิม</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">• กรอกรหัสสินค้าที่มีอยู่แล้ว = อัปเดตของเดิม จำนวนจะถูกบวกเพิ่มเข้าคลัง และแก้ต้นทุน/ราคาให้</t>
+          <t xml:space="preserve">  จำนวนจะถูกบวกเพิ่มเข้าคลัง และแก้ต้นทุน/ราคาให้</t>
         </is>
       </c>
     </row>
@@ -319,33 +319,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">• บาร์โค้ด — เว้นว่างไว้ ระบบจะใช้รหัสสินค้าเป็นบาร์โค้ด</t>
+          <t xml:space="preserve">• ถ้าไม่ตรงกับอะไรเลย = สินค้าใหม่ เว้นรหัสว่างไว้ ระบบจะออกรหัสให้ (P0001, P0002, ...)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">• หน่วย — เว้นว่างไว้ ระบบจะใช้ "pcs" (ชิ้น) ถ้ากรอกหน่วยที่ไม่มีในระบบจะถูกเว้นว่าง</t>
+          <t xml:space="preserve">• ถ้ามีหลายแถวที่ชี้ไปสินค้าตัวเดียวกัน จำนวนจะถูกรวมเข้าด้วยกัน</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">• ราคาขายขั้นต่ำ — เว้นว่างไว้ ระบบจะคิดให้เป็น 90% ของราคาขาย และต้องไม่เกินราคาขาย</t>
+          <t xml:space="preserve">• บาร์โค้ด — เว้นว่างไว้ ระบบจะใช้รหัสสินค้าเป็นบาร์โค้ด</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">• จำนวนที่รับเข้าคลังหลัก — สินค้าใหม่เข้าคลังหลักเท่านั้น เว้นว่าง = 0</t>
+          <t xml:space="preserve">• หน่วย — เว้นว่างไว้ ระบบจะใช้ "pcs" (ชิ้น) ถ้ากรอกหน่วยที่ไม่มีในระบบจะถูกเว้นว่าง</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• ราคาขายขั้นต่ำ — เว้นว่างไว้ ระบบจะคิดให้เป็น 90% ของราคาขาย และต้องไม่เกินราคาขาย</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• จำนวนที่รับเข้าคลังหลัก — สินค้าใหม่เข้าคลังหลักเท่านั้น เว้นว่าง = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">• ห้ามแก้ไข ลบ หรือสลับหัวคอลัมน์ในแถวที่ 1 ของชีต "สินค้า"</t>
         </is>
